--- a/RAMON FRANCO/Octubre/PRORRATEO-RAMON-FRANCO-Octubre.xlsx
+++ b/RAMON FRANCO/Octubre/PRORRATEO-RAMON-FRANCO-Octubre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3C8885-400E-4B39-B19E-7F408C763104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E21873-7A1D-4F5E-9F46-8E9A76248DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="86">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -274,9 +274,6 @@
     <t>SERGIO</t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 15/10 LIQUIDACION: SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>Total a Pagar 2do vto</t>
   </si>
   <si>
@@ -284,6 +281,12 @@
   </si>
   <si>
     <t>Vto: 14/10</t>
+  </si>
+  <si>
+    <t>EXPENSAS - VENCIMIENTO 14/11 LIQUIDACION: OCTUBRE</t>
+  </si>
+  <si>
+    <t>NN</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1240,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="82" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B1" s="83"/>
       <c r="C1" s="83"/>
@@ -1395,7 +1398,7 @@
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
       <c r="P10" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q10" s="19"/>
     </row>
@@ -1446,10 +1449,10 @@
         <v>68</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1467,7 +1470,7 @@
         <v>7.99</v>
       </c>
       <c r="F12" s="74">
-        <v>372286.79460954876</v>
+        <v>486400.92506231263</v>
       </c>
       <c r="G12" s="75">
         <v>0</v>
@@ -1479,16 +1482,16 @@
       </c>
       <c r="J12" s="75">
         <f t="shared" ref="J12:J19" si="0">F12-G12-H12</f>
-        <v>372286.79460954876</v>
+        <v>486400.92506231263</v>
       </c>
       <c r="K12" s="75"/>
       <c r="L12" s="76">
         <f>IF(J11&gt;0,(J12+K12)*8%,0)</f>
-        <v>29782.943568763902</v>
+        <v>38912.074004985014</v>
       </c>
       <c r="M12" s="76">
         <f>J12+L12+K12</f>
-        <v>402069.73817831266</v>
+        <v>525312.99906729767</v>
       </c>
       <c r="N12" s="75">
         <f>C7*E12/100</f>
@@ -1500,11 +1503,11 @@
       </c>
       <c r="P12" s="75">
         <f>N12+M12+O12</f>
-        <v>486400.92506231263</v>
+        <v>609644.18595129764</v>
       </c>
       <c r="Q12" s="76">
         <f>P12*3%+P12</f>
-        <v>500992.95281418203</v>
+        <v>627933.51152983657</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1524,14 +1527,13 @@
         <v>6.05</v>
       </c>
       <c r="F13" s="58">
-        <v>100326.77187500001</v>
+        <v>63855.279179999998</v>
       </c>
       <c r="G13" s="44">
         <v>0</v>
       </c>
       <c r="H13" s="69">
-        <f t="shared" ref="H13:H18" si="2">F13</f>
-        <v>100326.77187500001</v>
+        <v>21175</v>
       </c>
       <c r="I13" s="44" t="e">
         <f>C9*E13/100</f>
@@ -1539,16 +1541,16 @@
       </c>
       <c r="J13" s="44">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>42680.279179999998</v>
       </c>
       <c r="K13" s="44"/>
       <c r="L13" s="45">
         <f>IF(J12&gt;0,(J13+K13)*8%,0)</f>
-        <v>0</v>
+        <v>3414.4223343999997</v>
       </c>
       <c r="M13" s="45">
-        <f t="shared" ref="M13:M15" si="3">J13+L13+K13</f>
-        <v>0</v>
+        <f t="shared" ref="M13:M15" si="2">J13+L13+K13</f>
+        <v>46094.701514399996</v>
       </c>
       <c r="N13" s="44">
         <f>C7*E13/100</f>
@@ -1559,12 +1561,12 @@
         <v>21175</v>
       </c>
       <c r="P13" s="77">
-        <f t="shared" ref="P13:P29" si="4">N13+M13+O13</f>
-        <v>63855.279179999998</v>
+        <f t="shared" ref="P13:P29" si="3">N13+M13+O13</f>
+        <v>109949.9806944</v>
       </c>
       <c r="Q13" s="78">
-        <f t="shared" ref="Q13:Q29" si="5">P13*3%+P13</f>
-        <v>65770.9375554</v>
+        <f t="shared" ref="Q13:Q29" si="4">P13*3%+P13</f>
+        <v>113248.480115232</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1584,14 +1586,14 @@
         <v>6.02</v>
       </c>
       <c r="F14" s="58">
-        <v>99829.283750000002</v>
+        <v>63538.641431999989</v>
       </c>
       <c r="G14" s="44">
         <v>0</v>
       </c>
       <c r="H14" s="69">
-        <f t="shared" si="2"/>
-        <v>99829.283750000002</v>
+        <f t="shared" ref="H13:H18" si="5">F14</f>
+        <v>63538.641431999989</v>
       </c>
       <c r="I14" s="44" t="e">
         <f>C9*E14/100</f>
@@ -1607,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N14" s="44">
@@ -1619,11 +1621,11 @@
         <v>21070</v>
       </c>
       <c r="P14" s="77">
+        <f t="shared" si="3"/>
+        <v>63538.641431999989</v>
+      </c>
+      <c r="Q14" s="78">
         <f t="shared" si="4"/>
-        <v>63538.641431999989</v>
-      </c>
-      <c r="Q14" s="78">
-        <f t="shared" si="5"/>
         <v>65444.800674959988</v>
       </c>
     </row>
@@ -1642,12 +1644,12 @@
         <v>7.63</v>
       </c>
       <c r="F15" s="60">
-        <v>126527.813125</v>
+        <v>80531.533907999983</v>
       </c>
       <c r="G15" s="46"/>
       <c r="H15" s="69">
-        <f t="shared" si="2"/>
-        <v>126527.813125</v>
+        <f t="shared" si="5"/>
+        <v>80531.533907999983</v>
       </c>
       <c r="I15" s="44" t="e">
         <f>C9*E15/100</f>
@@ -1663,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N15" s="50">
@@ -1675,11 +1677,11 @@
         <v>26705</v>
       </c>
       <c r="P15" s="77">
+        <f t="shared" si="3"/>
+        <v>80531.533907999983</v>
+      </c>
+      <c r="Q15" s="78">
         <f t="shared" si="4"/>
-        <v>80531.533907999983</v>
-      </c>
-      <c r="Q15" s="78">
-        <f t="shared" si="5"/>
         <v>82947.479925239983</v>
       </c>
     </row>
@@ -1700,31 +1702,28 @@
         <v>6.05</v>
       </c>
       <c r="F16" s="58">
-        <v>100326.77187500001</v>
+        <v>63855.279179999998</v>
       </c>
       <c r="G16" s="46">
         <v>0</v>
       </c>
-      <c r="H16" s="69">
-        <f t="shared" si="2"/>
-        <v>100326.77187500001</v>
-      </c>
+      <c r="H16" s="69"/>
       <c r="I16" s="44" t="e">
         <f>C9*E16/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J16" s="44">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>63855.279179999998</v>
       </c>
       <c r="K16" s="44"/>
       <c r="L16" s="45">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5108.4223344000002</v>
       </c>
       <c r="M16" s="45">
         <f>J16+L16+K16</f>
-        <v>0</v>
+        <v>68963.701514400003</v>
       </c>
       <c r="N16" s="44">
         <f>C7*E16/100</f>
@@ -1735,12 +1734,12 @@
         <v>21175</v>
       </c>
       <c r="P16" s="77">
+        <f t="shared" si="3"/>
+        <v>132818.9806944</v>
+      </c>
+      <c r="Q16" s="78">
         <f t="shared" si="4"/>
-        <v>63855.279179999998</v>
-      </c>
-      <c r="Q16" s="78">
-        <f t="shared" si="5"/>
-        <v>65770.9375554</v>
+        <v>136803.55011523201</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1760,31 +1759,28 @@
         <v>6.02</v>
       </c>
       <c r="F17" s="58">
-        <v>99829.283750000002</v>
+        <v>63538.641431999989</v>
       </c>
       <c r="G17" s="44">
         <v>0</v>
       </c>
-      <c r="H17" s="69">
-        <f t="shared" si="2"/>
-        <v>99829.283750000002</v>
-      </c>
+      <c r="H17" s="69"/>
       <c r="I17" s="44" t="e">
         <f>C9*E17/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J17" s="44">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>63538.641431999989</v>
       </c>
       <c r="K17" s="44"/>
       <c r="L17" s="45">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5083.0913145599989</v>
       </c>
       <c r="M17" s="45">
         <f t="shared" ref="M17:M29" si="7">J17+L17+K17</f>
-        <v>0</v>
+        <v>68621.732746559981</v>
       </c>
       <c r="N17" s="44">
         <f>C7*E17/100</f>
@@ -1795,12 +1791,12 @@
         <v>21070</v>
       </c>
       <c r="P17" s="77">
+        <f t="shared" si="3"/>
+        <v>132160.37417855999</v>
+      </c>
+      <c r="Q17" s="78">
         <f t="shared" si="4"/>
-        <v>63538.641431999989</v>
-      </c>
-      <c r="Q17" s="78">
-        <f t="shared" si="5"/>
-        <v>65444.800674959988</v>
+        <v>136125.18540391678</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1818,14 +1814,14 @@
         <v>7.63</v>
       </c>
       <c r="F18" s="58">
-        <v>126527.813125</v>
+        <v>80531.533907999983</v>
       </c>
       <c r="G18" s="44">
         <v>0</v>
       </c>
       <c r="H18" s="69">
-        <f t="shared" si="2"/>
-        <v>126527.813125</v>
+        <f t="shared" si="5"/>
+        <v>80531.533907999983</v>
       </c>
       <c r="I18" s="44" t="e">
         <f>C9*E18/100</f>
@@ -1853,11 +1849,11 @@
         <v>26705</v>
       </c>
       <c r="P18" s="77">
+        <f t="shared" si="3"/>
+        <v>80531.533907999983</v>
+      </c>
+      <c r="Q18" s="78">
         <f t="shared" si="4"/>
-        <v>80531.533907999983</v>
-      </c>
-      <c r="Q18" s="78">
-        <f t="shared" si="5"/>
         <v>82947.479925239983</v>
       </c>
     </row>
@@ -1876,7 +1872,7 @@
         <v>6.05</v>
       </c>
       <c r="F19" s="58">
-        <v>182107.6076468</v>
+        <v>260531.49543854402</v>
       </c>
       <c r="G19" s="44">
         <v>0</v>
@@ -1888,16 +1884,16 @@
       </c>
       <c r="J19" s="44">
         <f t="shared" si="0"/>
-        <v>182107.6076468</v>
+        <v>260531.49543854402</v>
       </c>
       <c r="K19" s="44"/>
       <c r="L19" s="45">
         <f t="shared" si="6"/>
-        <v>14568.608611743999</v>
+        <v>20842.519635083521</v>
       </c>
       <c r="M19" s="45">
         <f t="shared" si="7"/>
-        <v>196676.21625854401</v>
+        <v>281374.01507362752</v>
       </c>
       <c r="N19" s="44">
         <f>C7*E19/100</f>
@@ -1908,12 +1904,12 @@
         <v>21175</v>
       </c>
       <c r="P19" s="77">
+        <f t="shared" si="3"/>
+        <v>345229.29425362754</v>
+      </c>
+      <c r="Q19" s="78">
         <f t="shared" si="4"/>
-        <v>260531.49543854402</v>
-      </c>
-      <c r="Q19" s="78">
-        <f t="shared" si="5"/>
-        <v>268347.44030170032</v>
+        <v>355586.17308123637</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1931,14 +1927,14 @@
         <v>6.02</v>
       </c>
       <c r="F20" s="58">
-        <v>45829.283750000002</v>
+        <v>63538.641431999989</v>
       </c>
       <c r="G20" s="44">
         <v>0</v>
       </c>
       <c r="H20" s="69">
         <f>F20</f>
-        <v>45829.283750000002</v>
+        <v>63538.641431999989</v>
       </c>
       <c r="I20" s="44" t="e">
         <f>C9*E20/100</f>
@@ -1966,11 +1962,11 @@
         <v>21070</v>
       </c>
       <c r="P20" s="77">
+        <f t="shared" si="3"/>
+        <v>63538.641431999989</v>
+      </c>
+      <c r="Q20" s="78">
         <f t="shared" si="4"/>
-        <v>63538.641431999989</v>
-      </c>
-      <c r="Q20" s="78">
-        <f t="shared" si="5"/>
         <v>65444.800674959988</v>
       </c>
     </row>
@@ -1989,14 +1985,14 @@
         <v>21.2</v>
       </c>
       <c r="F21" s="58">
-        <v>351558.27500000002</v>
+        <v>223757.34191999998</v>
       </c>
       <c r="G21" s="44">
         <v>0</v>
       </c>
       <c r="H21" s="69">
-        <f>F21</f>
-        <v>351558.27500000002</v>
+        <f>F21-74200</f>
+        <v>149557.34191999998</v>
       </c>
       <c r="I21" s="44" t="e">
         <f>C9*E21/100</f>
@@ -2004,16 +2000,16 @@
       </c>
       <c r="J21" s="44">
         <f t="shared" ref="J21:J29" si="8">F21-G21-H21</f>
-        <v>0</v>
+        <v>74200</v>
       </c>
       <c r="K21" s="44"/>
       <c r="L21" s="45">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5936</v>
       </c>
       <c r="M21" s="45">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>80136</v>
       </c>
       <c r="N21" s="44">
         <f>C7*E21/100</f>
@@ -2024,12 +2020,12 @@
         <v>74200</v>
       </c>
       <c r="P21" s="77">
+        <f t="shared" si="3"/>
+        <v>303893.34191999998</v>
+      </c>
+      <c r="Q21" s="78">
         <f t="shared" si="4"/>
-        <v>223757.34191999998</v>
-      </c>
-      <c r="Q21" s="78">
-        <f t="shared" si="5"/>
-        <v>230470.06217759999</v>
+        <v>313010.14217759995</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2049,31 +2045,28 @@
         <v>6.81</v>
       </c>
       <c r="F22" s="58">
-        <v>112929.80437500001</v>
+        <v>71876.768795999989</v>
       </c>
       <c r="G22" s="44">
         <v>0</v>
       </c>
-      <c r="H22" s="69">
-        <f>F22</f>
-        <v>112929.80437500001</v>
-      </c>
+      <c r="H22" s="69"/>
       <c r="I22" s="44" t="e">
         <f>C9*E22/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J22" s="44">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>71876.768795999989</v>
       </c>
       <c r="K22" s="44"/>
       <c r="L22" s="45">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5750.141503679999</v>
       </c>
       <c r="M22" s="45">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>77626.910299679992</v>
       </c>
       <c r="N22" s="44">
         <f>C7*E22/100</f>
@@ -2084,12 +2077,12 @@
         <v>23835</v>
       </c>
       <c r="P22" s="77">
+        <f t="shared" si="3"/>
+        <v>149503.67909567998</v>
+      </c>
+      <c r="Q22" s="78">
         <f t="shared" si="4"/>
-        <v>71876.768795999989</v>
-      </c>
-      <c r="Q22" s="78">
-        <f t="shared" si="5"/>
-        <v>74033.071859879987</v>
+        <v>153988.78946855039</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2109,29 +2102,29 @@
         <v>6.52</v>
       </c>
       <c r="F23" s="69">
-        <v>108120.7525</v>
+        <v>118106.869932</v>
       </c>
       <c r="G23" s="44">
         <v>0</v>
       </c>
       <c r="H23" s="69">
-        <v>62481</v>
+        <v>45996</v>
       </c>
       <c r="I23" s="44">
         <v>0</v>
       </c>
       <c r="J23" s="44">
         <f t="shared" si="8"/>
-        <v>45639.752500000002</v>
+        <v>72110.869932000001</v>
       </c>
       <c r="K23" s="44"/>
       <c r="L23" s="67">
         <f t="shared" si="6"/>
-        <v>3651.1802000000002</v>
+        <v>5768.8695945600002</v>
       </c>
       <c r="M23" s="67">
         <f>J23+L23+K23</f>
-        <v>49290.932700000005</v>
+        <v>77879.739526560006</v>
       </c>
       <c r="N23" s="44">
         <f>C7*E23/100</f>
@@ -2142,12 +2135,12 @@
         <v>22820</v>
       </c>
       <c r="P23" s="77">
+        <f t="shared" si="3"/>
+        <v>146695.67675856</v>
+      </c>
+      <c r="Q23" s="78">
         <f t="shared" si="4"/>
-        <v>118106.869932</v>
-      </c>
-      <c r="Q23" s="78">
-        <f t="shared" si="5"/>
-        <v>121650.07602996001</v>
+        <v>151096.54706131681</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2165,7 +2158,7 @@
         <v>1.18</v>
       </c>
       <c r="F24" s="74">
-        <v>592508.98202045681</v>
+        <v>652364.11867009336</v>
       </c>
       <c r="G24" s="75">
         <v>0</v>
@@ -2177,16 +2170,16 @@
       </c>
       <c r="J24" s="75">
         <f t="shared" si="8"/>
-        <v>592508.98202045681</v>
+        <v>652364.11867009336</v>
       </c>
       <c r="K24" s="75"/>
       <c r="L24" s="76">
         <f t="shared" si="6"/>
-        <v>47400.718561636546</v>
+        <v>52189.12949360747</v>
       </c>
       <c r="M24" s="76">
         <f t="shared" si="7"/>
-        <v>639909.70058209333</v>
+        <v>704553.2481637008</v>
       </c>
       <c r="N24" s="75">
         <f>C7*E24/100</f>
@@ -2197,12 +2190,12 @@
         <v>4130</v>
       </c>
       <c r="P24" s="75">
+        <f t="shared" si="3"/>
+        <v>717007.66625170084</v>
+      </c>
+      <c r="Q24" s="76">
         <f t="shared" si="4"/>
-        <v>652364.11867009336</v>
-      </c>
-      <c r="Q24" s="76">
-        <f t="shared" si="5"/>
-        <v>671935.04223019618</v>
+        <v>738517.89623925183</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2220,7 +2213,7 @@
         <v>1.17</v>
       </c>
       <c r="F25" s="74">
-        <v>584971.97717473609</v>
+        <v>644118.60752071498</v>
       </c>
       <c r="G25" s="75">
         <v>0</v>
@@ -2234,16 +2227,16 @@
       </c>
       <c r="J25" s="75">
         <f t="shared" si="8"/>
-        <v>584971.97717473609</v>
+        <v>644118.60752071498</v>
       </c>
       <c r="K25" s="75"/>
       <c r="L25" s="76">
         <f t="shared" si="6"/>
-        <v>46797.758173978887</v>
+        <v>51529.488601657198</v>
       </c>
       <c r="M25" s="76">
         <f t="shared" si="7"/>
-        <v>631769.73534871498</v>
+        <v>695648.0961223722</v>
       </c>
       <c r="N25" s="75">
         <f>C7*E25/100</f>
@@ -2254,125 +2247,123 @@
         <v>4095</v>
       </c>
       <c r="P25" s="75">
+        <f t="shared" si="3"/>
+        <v>707996.9682943722</v>
+      </c>
+      <c r="Q25" s="76">
         <f t="shared" si="4"/>
-        <v>644118.60752071498</v>
-      </c>
-      <c r="Q25" s="76">
-        <f t="shared" si="5"/>
-        <v>663442.16574633645</v>
+        <v>729236.87734320341</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>16</v>
       </c>
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="64" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="64"/>
-      <c r="E26" s="43">
+      <c r="C26" s="72" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="72"/>
+      <c r="E26" s="73">
         <v>1.06</v>
       </c>
-      <c r="F26" s="58">
-        <v>17577.91375</v>
-      </c>
-      <c r="G26" s="44">
-        <v>0</v>
-      </c>
-      <c r="H26" s="69">
-        <f>F26</f>
-        <v>17577.91375</v>
-      </c>
-      <c r="I26" s="44" t="e">
+      <c r="F26" s="74">
+        <f>14989+13267+17578+11187.867096</f>
+        <v>57021.867096000002</v>
+      </c>
+      <c r="G26" s="75">
+        <v>0</v>
+      </c>
+      <c r="H26" s="74"/>
+      <c r="I26" s="75" t="e">
         <f>C9*E26/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J26" s="44">
+      <c r="J26" s="75">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="44"/>
-      <c r="L26" s="45">
+        <v>57021.867096000002</v>
+      </c>
+      <c r="K26" s="75"/>
+      <c r="L26" s="76">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="45">
+        <v>4561.7493676800004</v>
+      </c>
+      <c r="M26" s="76">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="44">
+        <v>61583.616463680002</v>
+      </c>
+      <c r="N26" s="75">
         <f>C7*E26/100</f>
         <v>7477.867095999999</v>
       </c>
-      <c r="O26" s="44">
+      <c r="O26" s="75">
         <f t="shared" si="1"/>
         <v>3710</v>
       </c>
-      <c r="P26" s="77">
+      <c r="P26" s="75">
+        <f t="shared" si="3"/>
+        <v>72771.483559679997</v>
+      </c>
+      <c r="Q26" s="76">
         <f t="shared" si="4"/>
-        <v>11187.867095999998</v>
-      </c>
-      <c r="Q26" s="78">
-        <f t="shared" si="5"/>
-        <v>11523.503108879999</v>
+        <v>74954.628066470395</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>17</v>
       </c>
-      <c r="B27" s="52" t="s">
+      <c r="B27" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="D27" s="64"/>
-      <c r="E27" s="43">
+      <c r="D27" s="72"/>
+      <c r="E27" s="73">
         <v>0.51</v>
       </c>
-      <c r="F27" s="58">
-        <v>55474.322412053785</v>
-      </c>
-      <c r="G27" s="44">
-        <v>0</v>
-      </c>
-      <c r="H27" s="69"/>
-      <c r="I27" s="44" t="e">
+      <c r="F27" s="74">
+        <v>65295.109921018091</v>
+      </c>
+      <c r="G27" s="75">
+        <v>0</v>
+      </c>
+      <c r="H27" s="74"/>
+      <c r="I27" s="75" t="e">
         <f>C9*E27/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J27" s="44">
+      <c r="J27" s="75">
         <f t="shared" si="8"/>
-        <v>55474.322412053785</v>
-      </c>
-      <c r="K27" s="44"/>
-      <c r="L27" s="45">
+        <v>65295.109921018091</v>
+      </c>
+      <c r="K27" s="75"/>
+      <c r="L27" s="76">
         <f t="shared" si="6"/>
-        <v>4437.9457929643031</v>
-      </c>
-      <c r="M27" s="45">
+        <v>5223.6087936814474</v>
+      </c>
+      <c r="M27" s="76">
         <f t="shared" si="7"/>
-        <v>59912.268205018088</v>
-      </c>
-      <c r="N27" s="44">
+        <v>70518.718714699542</v>
+      </c>
+      <c r="N27" s="75">
         <f>C7*E27/100</f>
         <v>3597.8417159999995</v>
       </c>
-      <c r="O27" s="44">
+      <c r="O27" s="75">
         <f t="shared" si="1"/>
         <v>1785</v>
       </c>
-      <c r="P27" s="77">
+      <c r="P27" s="75">
+        <f t="shared" si="3"/>
+        <v>75901.560430699537</v>
+      </c>
+      <c r="Q27" s="76">
         <f t="shared" si="4"/>
-        <v>65295.109921018091</v>
-      </c>
-      <c r="Q27" s="78">
-        <f t="shared" si="5"/>
-        <v>67253.963218648627</v>
+        <v>78178.607243620529</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2390,14 +2381,14 @@
         <v>0.27</v>
       </c>
       <c r="F28" s="58">
-        <v>4477.3931250000005</v>
+        <v>2849.739732</v>
       </c>
       <c r="G28" s="44">
         <v>0</v>
       </c>
       <c r="H28" s="69">
         <f>F28</f>
-        <v>4477.3931250000005</v>
+        <v>2849.739732</v>
       </c>
       <c r="I28" s="44" t="e">
         <f>C9*E28/100</f>
@@ -2425,11 +2416,11 @@
         <v>945</v>
       </c>
       <c r="P28" s="77">
+        <f t="shared" si="3"/>
+        <v>2849.739732</v>
+      </c>
+      <c r="Q28" s="78">
         <f t="shared" si="4"/>
-        <v>2849.739732</v>
-      </c>
-      <c r="Q28" s="78">
-        <f t="shared" si="5"/>
         <v>2935.2319239600001</v>
       </c>
     </row>
@@ -2446,28 +2437,25 @@
         <v>1.82</v>
       </c>
       <c r="F29" s="59">
-        <v>30180.946250000001</v>
+        <v>19209.356712000001</v>
       </c>
       <c r="G29" s="44">
         <v>0</v>
       </c>
-      <c r="H29" s="69">
-        <f>F29</f>
-        <v>30180.946250000001</v>
-      </c>
+      <c r="H29" s="69"/>
       <c r="I29" s="48"/>
       <c r="J29" s="44">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19209.356712000001</v>
       </c>
       <c r="K29" s="48"/>
       <c r="L29" s="45">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1536.7485369600001</v>
       </c>
       <c r="M29" s="45">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20746.105248960001</v>
       </c>
       <c r="N29" s="48">
         <f>C7*E29/100</f>
@@ -2478,12 +2466,12 @@
         <v>6370</v>
       </c>
       <c r="P29" s="77">
+        <f t="shared" si="3"/>
+        <v>39955.461960960005</v>
+      </c>
+      <c r="Q29" s="78">
         <f t="shared" si="4"/>
-        <v>19209.356712000001</v>
-      </c>
-      <c r="Q29" s="78">
-        <f t="shared" si="5"/>
-        <v>19785.63741336</v>
+        <v>41154.125819788802</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="2" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
@@ -2496,7 +2484,7 @@
       <c r="E30" s="42"/>
       <c r="F30" s="54">
         <f>SUM(F12:F29)</f>
-        <v>3111391.7901135953</v>
+        <v>3080921.751272683</v>
       </c>
       <c r="G30" s="54">
         <f>SUM(G12:G29)</f>
@@ -2504,17 +2492,17 @@
       </c>
       <c r="H30" s="62">
         <f>SUM(H12:H29)</f>
-        <v>1278402.3537500002</v>
+        <v>507718.43233199988</v>
       </c>
       <c r="I30" s="54"/>
       <c r="J30" s="62">
         <f>SUM(J12:J29)</f>
-        <v>1832989.4363635955</v>
+        <v>2573203.3189406828</v>
       </c>
       <c r="K30" s="54"/>
       <c r="L30" s="68">
         <f>L12+L13+L14+L15+L16+L17+L18+L19+L20+L21+L22+L23+L24+L25+L26+L27+L28+L29</f>
-        <v>146639.15490908764</v>
+        <v>205856.26551525466</v>
       </c>
       <c r="M30" s="55"/>
       <c r="N30" s="70">
@@ -2527,11 +2515,11 @@
       </c>
       <c r="P30" s="57">
         <f>SUM(P16:P29) +P15+P14+P13+P12</f>
-        <v>3035087.751272683</v>
+        <v>3834518.7444559382</v>
       </c>
       <c r="Q30" s="57">
         <f>SUM(Q16:Q29) +Q15+Q14+Q13+Q12</f>
-        <v>3126140.3838108638</v>
+        <v>3949554.3067896161</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
